--- a/prius2/input/technisch_vademecum_v25-08-19.xlsx
+++ b/prius2/input/technisch_vademecum_v25-08-19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bram_dhondt\Documents\GitHub\prius\prius2\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7F8958-027B-450C-AE3F-EC61706E0B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C9F01B-F195-4FFB-AFBC-43C10E59FC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="readme" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
   <si>
     <t>groep</t>
   </si>
@@ -37,9 +37,6 @@
     <t>GBIF_codes</t>
   </si>
   <si>
-    <t>mahonie</t>
-  </si>
-  <si>
     <t>rimpelroos</t>
   </si>
   <si>
@@ -64,39 +61,21 @@
     <t>vad</t>
   </si>
   <si>
-    <t>grote kroosvaren</t>
-  </si>
-  <si>
     <t>gele maskerbloem</t>
   </si>
   <si>
     <t>reuzenbalsemien</t>
   </si>
   <si>
-    <t>douglaspluimspirea</t>
-  </si>
-  <si>
-    <t>Chinese bruidsluier</t>
-  </si>
-  <si>
-    <t>Cyperus eragrostis</t>
-  </si>
-  <si>
     <t>Spaanse hyacint</t>
   </si>
   <si>
     <t>Hyacinthoides ×massartiana</t>
   </si>
   <si>
-    <t>dijkviltbraam</t>
-  </si>
-  <si>
     <t>hemelboom</t>
   </si>
   <si>
-    <t>alsemambrosia</t>
-  </si>
-  <si>
     <t>struikaster</t>
   </si>
   <si>
@@ -106,18 +85,12 @@
     <t>hottentotvijg</t>
   </si>
   <si>
-    <t>pampagras</t>
-  </si>
-  <si>
     <t>watercrassula</t>
   </si>
   <si>
     <t>egeria</t>
   </si>
   <si>
-    <t>smalle olijfwilg</t>
-  </si>
-  <si>
     <t>smalle waterpest</t>
   </si>
   <si>
@@ -145,12 +118,6 @@
     <t>ongelijkbladig vederkruid</t>
   </si>
   <si>
-    <t>valse wingerd</t>
-  </si>
-  <si>
-    <t>vijfbladige wingerd</t>
-  </si>
-  <si>
     <t>moerashyacint</t>
   </si>
   <si>
@@ -164,9 +131,6 @@
   </si>
   <si>
     <t>Sachalinse duizendknoop</t>
-  </si>
-  <si>
-    <t>gele ribes</t>
   </si>
   <si>
     <t>grote vlotvaren</t>
@@ -218,8 +182,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -500,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="32.109375" bestFit="1" customWidth="1"/>
@@ -509,624 +473,428 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>8002952</v>
+        <v>5389029</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>5389029</v>
+        <v>5329260</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>5389029</v>
+        <v>7346102</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>5334351</v>
+        <v>5274863</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>5334351</v>
+        <v>7978544</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>2715482</v>
+        <v>3190653</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>2996525</v>
+        <v>3084842</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>3027159</v>
+        <v>5304294</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>5329260</v>
+        <v>2889173</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>7346102</v>
+        <v>4038485</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>2986111</v>
+        <v>5420991</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
         <v>5</v>
       </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>2650107</v>
+        <v>5389017</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>5274863</v>
+        <v>5384932</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>7978544</v>
+        <v>2869311</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>3190653</v>
+        <v>2766030</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>3084842</v>
+        <v>5361762</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>5304294</v>
+        <v>5361785</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>2889173</v>
+        <v>2891770</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>4038485</v>
+        <v>3034825</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>5420991</v>
+        <v>3003979</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>5389017</v>
+        <v>2889088</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>5384932</v>
+        <v>5329212</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>3033865</v>
+        <v>5304257</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>2869311</v>
+        <v>3129663</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26">
-        <v>2766030</v>
+        <v>2865565</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27">
-        <v>5361762</v>
+        <v>5362054</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>2704523</v>
+        <v>2765942</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>5361785</v>
+        <v>5421039</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30">
-        <v>2891770</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>3034825</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>3003979</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>2889088</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>3039269</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>5329212</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>5304257</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>3129663</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>3039203</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>2865565</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>3039194</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>5</v>
-      </c>
-      <c r="B41" t="s">
-        <v>27</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>5362054</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>5</v>
-      </c>
-      <c r="B42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>2765942</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43">
-        <v>5421039</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
         <v>2882443</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D53">
-    <sortCondition ref="B2:B53"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D42">
+    <sortCondition ref="B2:B42"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1143,21 +911,21 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>45883</v>
       </c>
     </row>
